--- a/clients/yeri/feedback/피드백-작성-양식.xlsx
+++ b/clients/yeri/feedback/피드백-작성-양식.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>테마 색상 변경 — '모던 차콜 &amp; 소프트 피치 핑크': 배경 화이트 유지, 브랜드색 차콜 그레이(#2D3748), 포인트 뮤트 핑크/피치(#E5A99E). 젊은 뷰티·디자인 고객 타겟의 트렌디한 느낌</t>
+          <t>사이트 색상 테마를 바꿉니다. 지금의 남색+금색 조합 대신 → 배경은 흰색 유지, 주요 색은 차콜 그레이(#2D3748), 포인트 색은 연한 피치 핑크(#E5A99E). 젊은 뷰티·디자인 분야 고객이 타겟이라 트렌디한 분위기를 원함 (참고 사이트와 같은 느낌).</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>메뉴 재구성: 홈/소개/서비스/상담 + LinkedIn 링크 추가 + 언어 전환(한/영/중) 추가</t>
+          <t>상단 메뉴에 두 가지를 추가합니다: ① LinkedIn 바로가기 ② 언어 전환 버튼(한/영/중). 기존 메뉴 4개(홈·소개·서비스·상담)는 그대로 둡니다.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>언어별 연동 — 원문: '한국어클릭은 블로그연동/ 중한은 링크드인연동'. 언어 전환이 번역 페이지가 아니라 외부 채널(블로그/링크드인) 연결인지, 연결 주소는 무엇인지 확인 필요</t>
+          <t>언어 버튼(한/영/중)을 눌렀을 때의 동작이 불분명합니다. 번역된 페이지로 바뀌는 게 아니라 외부 채널로 이동하는 것으로 보임 (원문: '한국어클릭은 블로그연동/ 중한은 링크드인연동'). 어느 언어가 어디로 연결되는지, 블로그·링크드인 주소가 무엇인지 답변을 기다리는 중.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>현재(오예리) 골격 유지 + 유레카 등 참조 사이트의 콘텐츠 요소 추가</t>
+          <t>지금 사이트의 뼈대(페이지 구성)는 유지하되, 참고 사이트들(유레카 특허법률사무소 등)에 있는 콘텐츠 요소들을 참고해서 내용을 더 풍부하게 보강해 달라는 요청.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>히어로 문구 후보: '꿈을 현실로 만들어 드립니다' — 원문에 물음표가 붙어 있어 확정 문구인지 확인 필요</t>
+          <t>메인 배너 제목 후보로 '꿈을 현실로 만들어 드립니다'가 제시됨. 다만 원문에 물음표가 붙어 있어 확정 문구인지 답변을 기다리는 중.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>차별점 3가지 노출: ① 출원–법률자문–소송–투자유치 자료까지 변호사·변리사 1:1 ② 전문성(의료·뷰티·디자인) ③ 영어·중국어 소통 가능</t>
+          <t>메인 배너 근처에 이 사무소만의 차별점 3가지를 보여줍니다: ① 출원부터 법률자문·소송·투자유치 자료까지 변호사+변리사가 1:1 전담 ② 의료·뷰티·디자인 분야 전문성 ③ 영어·중국어 상담 가능.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>'무료 상담 신청' → '상담 신청'으로 변경 — '무료' 표현 전체 제거 (상담 유료화 항목과 연동)</t>
+          <t>사이트 전체에서 '무료 상담' 표현을 없애고 '상담 신청'으로 바꿉니다. 이유: 상담이 유료로 바뀌기 때문 (19번 상담 정책 변경과 한 세트).</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>수치 4칸 컨테이너 유지, 내용 교체: ① 의료&amp;IP 전략(전문성) ② 영어·중국어(소통가능) ③ 9년+(실무경력) ④ 네 번째 칸 내용 미정('칸 남겨줘') — 4번째 칸 내용 확인 필요</t>
+          <t>실적 수치 4칸의 디자인(칸 구성)은 유지하고 내용만 바꿉니다: ① 전문성 → '의료 &amp; IP 전략' ② 소통 → '영어·중국어 가능' ③ 실무 경력 → '9년+' ④ 네 번째 칸은 내용 미정 (원문: '칸 남겨줘') — 답변을 기다리는 중.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>업무분야 문구 변경 — 여섯 개 분야 개수는 유지 (서비스 재편 항목과 연동)</t>
+          <t>업무 분야 카드 6개의 제목·설명 문구를 새 서비스 구성(17번 재편안)에 맞게 바꿉니다. 카드가 6개인 것은 그대로 유지.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>진행절차 구성 유지, 상담 비용 관련 문구만 수정 (무료 → 유료 정책 반영)</t>
+          <t>진행 절차 5단계 구성은 그대로 두고, '무료 상담 접수' 등 비용이 언급되는 문구만 유료 정책(19번)에 맞게 고칩니다.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>FAQ 구성 유지, 상담 비용 관련 답변만 수정 ('상담은 정말 무료인가요' 항목 등)</t>
+          <t>FAQ 6개 구성은 그대로 두고, '상담은 정말 무료인가요?' 등 비용 관련 답변만 유료 정책(19번)에 맞게 고칩니다.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>전화 채널 제거 → 카톡 상담 + 게시판 상담으로 한정. 사이트 전체의 전화번호 노출(헤더 CTA·푸터·플로팅)도 함께 정리</t>
+          <t>연락 수단에서 전화를 뺍니다. 카카오톡 상담과 게시판(상담 폼) 두 가지만 남기고, 헤더·푸터·플로팅 버튼 등 전화번호가 보이는 곳을 전부 정리합니다.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>기관/파트너 로고 섹션 추가: 특허청, 키프리스, 한국발명진흥회, 특허심판원, 특허법원, 칭화대</t>
+          <t>홈에 협력·관련 기관 로고를 나열하는 섹션을 새로 만듭니다: 특허청, 키프리스, 한국발명진흥회, 특허심판원, 특허법원, 칭화대. (칭화대 로고 이미지는 feedback 폴더에 첨부되어 있음)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>직함 변경: '오예리 대표 변호사·변리사' / 영문 'dual-qualified Attorney-at-Law &amp; Patent Attorney (Korea)'</t>
+          <t>대표 직함을 '오예리 대표 변호사·변리사'로 바꿉니다 (변호사 자격 추가). 영문 표기는 'dual-qualified Attorney-at-Law &amp; Patent Attorney (Korea)'.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>전문분야 추가: Medical Malpractice &amp; IP Strategy — [의료] 20년차 신경외과·영상의학과 전문의 자문, 의료소송·자문 리스트업 / [IP 전략] 중국 IP 금융 자문, 출원(수술도구·슬리퍼 등)·자문 리스트업 — 리스트 자료 고객 제공 필요</t>
+          <t>대표 프로필에 전문분야 '의료 &amp; IP 전략' 소개를 추가합니다. [의료] 20년차 신경외과·영상의학과 전문의 자문 경력, 의료소송·자문 사례 목록 / [IP 전략] 중국 IP 금융 자문, 출원 사례(수술도구·슬리퍼 등) 목록. 사례 목록 자료는 고객이 보내줘야 함 — 답변을 기다리는 중.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>저서 소개 섹션 추가 — 표지 이미지 클릭 시 무료배포 또는 구매 페이지로 연결 (연결 주소 확인 필요)</t>
+          <t>소개 페이지에 대표 저서 소개 섹션을 새로 만듭니다. 책 표지를 클릭하면 무료배포 페이지 또는 구매 페이지로 이동. 표지 이미지는 받았지만 연결할 주소가 없음 — 답변을 기다리는 중.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>서비스 6개 분야 재편: ① IP 등록(특허·상표·디자인·저작권, 비용·절차 명시) ② 해외출원 ③ 조사(선행기술조사·기술가치평가·기술이전·라이선스·시장조사) ④ 전략(특허맵·IP-R&amp;D 컨설팅·IP 포트폴리오, 국내외 진출/IR·투자유치) ⑤ 침해 대응 및 민·형사 소송(내용증명·가처분·병행수입·통관보류·권리범위확인심판 등) ⑥ 영업비밀·부정경쟁행위(전직금지가처분·비밀유지계약서 등)</t>
+          <t>서비스 6개 분야를 완전히 새로 짭니다. 지금: 특허/상표/디자인/심판/소송/해외출원 → 새 구성: ① IP 등록 (특허·상표·디자인·저작권 — 비용과 절차를 명시) ② 해외출원 ③ 조사 (선행기술조사 / 기술가치평가·기술이전·라이선스 컨설팅 / 시장조사) ④ 전략 (특허맵, IP-R&amp;D 컨설팅, IP 포트폴리오 설계 — 국내외 진출·투자유치 지원) ⑤ 침해 대응·민형사 소송 (경고장, 가처분, 병행수입·통관보류 분쟁, 권리범위확인심판 등) ⑥ 영업비밀·부정경쟁행위 (전직금지가처분, 비밀유지계약서 작성 등)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>등록 비용 표기: 특허 140 / 상표 빠른 20+20·기본 6+12 / 디자인 30+30 / 저작권 30 — 단위(만원 여부)와 표기 방식 확인 필요</t>
+          <t>등록 비용을 사이트에 표기합니다. 고객이 준 수치: 특허 140 / 상표는 빠른 심사 20+20, 기본 6+12 / 디자인 30+30 / 저작권 30. 단위가 만원인지, 두 숫자가 착수금+등록료인지 불분명 — 답변을 기다리는 중.</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>상담 정책 변경: 무료 → 변호사법 의거 기본 30분 5만원, 난이도 있는 사안은 타임차지 — 상담 페이지·CTA 배너·FAQ 등 '무료' 문구 전체 교체</t>
+          <t>상담 정책을 바꿉니다: 무료 상담 → 기본 30분 5만원(변호사법 근거), 복잡한 사안은 시간당 과금. 상담 페이지·하단 배너·FAQ 등 '무료'라고 안내하던 곳을 전부 새 정책으로 교체.</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>WIPO IP 교육과정 소개 자료가 첨부되어 있음 — 사이트에 반영할 내용인지 용도 확인 필요</t>
+          <t>받은 문서에 WIPO(세계지식재산기구) 교육과정 소개 글이 들어 있는데, 사이트에 쓰라는 건지 단순 참고용인지 알 수 없음 — 용도 답변을 기다리는 중.</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">

--- a/clients/yeri/feedback/피드백-작성-양식.xlsx
+++ b/clients/yeri/feedback/피드백-작성-양식.xlsx
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +73,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0010294C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
     <fill>
@@ -117,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -144,9 +149,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,7 +166,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,7 +175,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -738,9 +746,9 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -804,7 +812,7 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
@@ -874,7 +882,7 @@
           <t>B (가능하면)</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
@@ -972,7 +980,7 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
@@ -1197,7 +1205,7 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
@@ -1233,7 +1241,7 @@
           <t>B (가능하면)</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
@@ -1303,7 +1311,7 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
@@ -1370,1100 +1378,1100 @@
           <t>C (아이디어)</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n">
+      <c r="A22" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n">
+      <c r="A24" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n">
+      <c r="A26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n">
+      <c r="A28" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n">
+      <c r="A30" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n">
+      <c r="A32" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n">
+      <c r="A34" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n">
+      <c r="A36" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n">
+      <c r="A38" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n">
+      <c r="A39" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="n">
+      <c r="A40" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="9" t="n"/>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n">
+      <c r="A41" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="12" t="n"/>
       <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
+      <c r="F41" s="12" t="n"/>
+      <c r="G41" s="12" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n">
+      <c r="A42" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n">
+      <c r="A43" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="12" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="11" t="n"/>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="12" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n">
+      <c r="A44" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="n">
+      <c r="A45" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="12" t="n"/>
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="11" t="n"/>
+      <c r="F45" s="12" t="n"/>
+      <c r="G45" s="12" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n">
+      <c r="A46" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="9" t="n"/>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="n">
+      <c r="A47" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
+      <c r="B47" s="12" t="n"/>
+      <c r="C47" s="12" t="n"/>
       <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
-      <c r="F47" s="11" t="n"/>
-      <c r="G47" s="11" t="n"/>
+      <c r="F47" s="12" t="n"/>
+      <c r="G47" s="12" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="n">
+      <c r="A48" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="9" t="n"/>
-      <c r="C48" s="9" t="n"/>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="9" t="n"/>
-      <c r="G48" s="9" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="n">
+      <c r="A49" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="11" t="n"/>
+      <c r="B49" s="12" t="n"/>
+      <c r="C49" s="12" t="n"/>
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
-      <c r="F49" s="11" t="n"/>
-      <c r="G49" s="11" t="n"/>
+      <c r="F49" s="12" t="n"/>
+      <c r="G49" s="12" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="n">
+      <c r="A50" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="9" t="n"/>
-      <c r="C50" s="9" t="n"/>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="9" t="n"/>
-      <c r="G50" s="9" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="n">
+      <c r="A51" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="11" t="n"/>
-      <c r="C51" s="11" t="n"/>
+      <c r="B51" s="12" t="n"/>
+      <c r="C51" s="12" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="11" t="n"/>
-      <c r="G51" s="11" t="n"/>
+      <c r="F51" s="12" t="n"/>
+      <c r="G51" s="12" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="n">
+      <c r="A52" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="9" t="n"/>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="9" t="n"/>
-      <c r="G52" s="9" t="n"/>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="n">
+      <c r="A53" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="11" t="n"/>
-      <c r="C53" s="11" t="n"/>
+      <c r="B53" s="12" t="n"/>
+      <c r="C53" s="12" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="11" t="n"/>
-      <c r="G53" s="11" t="n"/>
+      <c r="F53" s="12" t="n"/>
+      <c r="G53" s="12" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="n">
+      <c r="A54" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="9" t="n"/>
-      <c r="C54" s="9" t="n"/>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="9" t="n"/>
-      <c r="G54" s="9" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="n">
+      <c r="A55" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="11" t="n"/>
-      <c r="C55" s="11" t="n"/>
+      <c r="B55" s="12" t="n"/>
+      <c r="C55" s="12" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="11" t="n"/>
-      <c r="G55" s="11" t="n"/>
+      <c r="F55" s="12" t="n"/>
+      <c r="G55" s="12" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="n">
+      <c r="A56" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="10" t="n"/>
-      <c r="E56" s="10" t="n"/>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="n">
+      <c r="A57" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="11" t="n"/>
-      <c r="C57" s="11" t="n"/>
+      <c r="B57" s="12" t="n"/>
+      <c r="C57" s="12" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="11" t="n"/>
-      <c r="G57" s="11" t="n"/>
+      <c r="F57" s="12" t="n"/>
+      <c r="G57" s="12" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="n">
+      <c r="A58" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="9" t="n"/>
-      <c r="C58" s="9" t="n"/>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="9" t="n"/>
-      <c r="G58" s="9" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="11" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="n">
+      <c r="A59" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="11" t="n"/>
-      <c r="C59" s="11" t="n"/>
+      <c r="B59" s="12" t="n"/>
+      <c r="C59" s="12" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="11" t="n"/>
-      <c r="G59" s="11" t="n"/>
+      <c r="F59" s="12" t="n"/>
+      <c r="G59" s="12" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="n">
+      <c r="A60" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="9" t="n"/>
-      <c r="C60" s="9" t="n"/>
-      <c r="D60" s="10" t="n"/>
-      <c r="E60" s="10" t="n"/>
-      <c r="F60" s="9" t="n"/>
-      <c r="G60" s="9" t="n"/>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="11" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="n">
+      <c r="A61" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="11" t="n"/>
-      <c r="C61" s="11" t="n"/>
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="12" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="11" t="n"/>
-      <c r="G61" s="11" t="n"/>
+      <c r="F61" s="12" t="n"/>
+      <c r="G61" s="12" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="n">
+      <c r="A62" s="10" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="9" t="n"/>
-      <c r="C62" s="9" t="n"/>
-      <c r="D62" s="10" t="n"/>
-      <c r="E62" s="10" t="n"/>
-      <c r="F62" s="9" t="n"/>
-      <c r="G62" s="9" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="11" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="n">
+      <c r="A63" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="11" t="n"/>
-      <c r="C63" s="11" t="n"/>
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="12" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="11" t="n"/>
-      <c r="G63" s="11" t="n"/>
+      <c r="F63" s="12" t="n"/>
+      <c r="G63" s="12" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="n">
+      <c r="A64" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="9" t="n"/>
-      <c r="C64" s="9" t="n"/>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="10" t="n"/>
-      <c r="F64" s="9" t="n"/>
-      <c r="G64" s="9" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="11" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="11" t="n">
+      <c r="A65" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="11" t="n"/>
-      <c r="C65" s="11" t="n"/>
+      <c r="B65" s="12" t="n"/>
+      <c r="C65" s="12" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="11" t="n"/>
-      <c r="G65" s="11" t="n"/>
+      <c r="F65" s="12" t="n"/>
+      <c r="G65" s="12" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="n">
+      <c r="A66" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="9" t="n"/>
-      <c r="C66" s="9" t="n"/>
-      <c r="D66" s="10" t="n"/>
-      <c r="E66" s="10" t="n"/>
-      <c r="F66" s="9" t="n"/>
-      <c r="G66" s="9" t="n"/>
+      <c r="B66" s="10" t="n"/>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="11" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="n">
+      <c r="A67" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="11" t="n"/>
-      <c r="C67" s="11" t="n"/>
+      <c r="B67" s="12" t="n"/>
+      <c r="C67" s="12" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
-      <c r="F67" s="11" t="n"/>
-      <c r="G67" s="11" t="n"/>
+      <c r="F67" s="12" t="n"/>
+      <c r="G67" s="12" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="n">
+      <c r="A68" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="9" t="n"/>
-      <c r="C68" s="9" t="n"/>
-      <c r="D68" s="10" t="n"/>
-      <c r="E68" s="10" t="n"/>
-      <c r="F68" s="9" t="n"/>
-      <c r="G68" s="9" t="n"/>
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="11" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="n">
+      <c r="A69" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="11" t="n"/>
-      <c r="C69" s="11" t="n"/>
+      <c r="B69" s="12" t="n"/>
+      <c r="C69" s="12" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
-      <c r="F69" s="11" t="n"/>
-      <c r="G69" s="11" t="n"/>
+      <c r="F69" s="12" t="n"/>
+      <c r="G69" s="12" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="n">
+      <c r="A70" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="9" t="n"/>
-      <c r="C70" s="9" t="n"/>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="9" t="n"/>
-      <c r="G70" s="9" t="n"/>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="11" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="11" t="n">
+      <c r="A71" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="11" t="n"/>
-      <c r="C71" s="11" t="n"/>
+      <c r="B71" s="12" t="n"/>
+      <c r="C71" s="12" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
-      <c r="F71" s="11" t="n"/>
-      <c r="G71" s="11" t="n"/>
+      <c r="F71" s="12" t="n"/>
+      <c r="G71" s="12" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="n">
+      <c r="A72" s="10" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="9" t="n"/>
-      <c r="C72" s="9" t="n"/>
-      <c r="D72" s="10" t="n"/>
-      <c r="E72" s="10" t="n"/>
-      <c r="F72" s="9" t="n"/>
-      <c r="G72" s="9" t="n"/>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="11" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="11" t="n">
+      <c r="A73" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="11" t="n"/>
-      <c r="C73" s="11" t="n"/>
+      <c r="B73" s="12" t="n"/>
+      <c r="C73" s="12" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="11" t="n"/>
-      <c r="G73" s="11" t="n"/>
+      <c r="F73" s="12" t="n"/>
+      <c r="G73" s="12" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="n">
+      <c r="A74" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="9" t="n"/>
-      <c r="C74" s="9" t="n"/>
-      <c r="D74" s="10" t="n"/>
-      <c r="E74" s="10" t="n"/>
-      <c r="F74" s="9" t="n"/>
-      <c r="G74" s="9" t="n"/>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="11" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="n">
+      <c r="A75" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="11" t="n"/>
-      <c r="C75" s="11" t="n"/>
+      <c r="B75" s="12" t="n"/>
+      <c r="C75" s="12" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
-      <c r="F75" s="11" t="n"/>
-      <c r="G75" s="11" t="n"/>
+      <c r="F75" s="12" t="n"/>
+      <c r="G75" s="12" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="n">
+      <c r="A76" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="9" t="n"/>
-      <c r="C76" s="9" t="n"/>
-      <c r="D76" s="10" t="n"/>
-      <c r="E76" s="10" t="n"/>
-      <c r="F76" s="9" t="n"/>
-      <c r="G76" s="9" t="n"/>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="11" t="n"/>
+      <c r="E76" s="11" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="n">
+      <c r="A77" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="11" t="n"/>
-      <c r="C77" s="11" t="n"/>
+      <c r="B77" s="12" t="n"/>
+      <c r="C77" s="12" t="n"/>
       <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
-      <c r="F77" s="11" t="n"/>
-      <c r="G77" s="11" t="n"/>
+      <c r="F77" s="12" t="n"/>
+      <c r="G77" s="12" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="n">
+      <c r="A78" s="10" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="9" t="n"/>
-      <c r="C78" s="9" t="n"/>
-      <c r="D78" s="10" t="n"/>
-      <c r="E78" s="10" t="n"/>
-      <c r="F78" s="9" t="n"/>
-      <c r="G78" s="9" t="n"/>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="11" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="11" t="n">
+      <c r="A79" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="11" t="n"/>
-      <c r="C79" s="11" t="n"/>
+      <c r="B79" s="12" t="n"/>
+      <c r="C79" s="12" t="n"/>
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="11" t="n"/>
-      <c r="G79" s="11" t="n"/>
+      <c r="F79" s="12" t="n"/>
+      <c r="G79" s="12" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="n">
+      <c r="A80" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="9" t="n"/>
-      <c r="C80" s="9" t="n"/>
-      <c r="D80" s="10" t="n"/>
-      <c r="E80" s="10" t="n"/>
-      <c r="F80" s="9" t="n"/>
-      <c r="G80" s="9" t="n"/>
+      <c r="B80" s="10" t="n"/>
+      <c r="C80" s="10" t="n"/>
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="11" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="n">
+      <c r="A81" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="11" t="n"/>
-      <c r="C81" s="11" t="n"/>
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="12" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="11" t="n"/>
-      <c r="G81" s="11" t="n"/>
+      <c r="F81" s="12" t="n"/>
+      <c r="G81" s="12" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="n">
+      <c r="A82" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="9" t="n"/>
-      <c r="C82" s="9" t="n"/>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="10" t="n"/>
-      <c r="F82" s="9" t="n"/>
-      <c r="G82" s="9" t="n"/>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="11" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="11" t="n">
+      <c r="A83" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="11" t="n"/>
-      <c r="C83" s="11" t="n"/>
+      <c r="B83" s="12" t="n"/>
+      <c r="C83" s="12" t="n"/>
       <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
-      <c r="F83" s="11" t="n"/>
-      <c r="G83" s="11" t="n"/>
+      <c r="F83" s="12" t="n"/>
+      <c r="G83" s="12" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="n">
+      <c r="A84" s="10" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="9" t="n"/>
-      <c r="C84" s="9" t="n"/>
-      <c r="D84" s="10" t="n"/>
-      <c r="E84" s="10" t="n"/>
-      <c r="F84" s="9" t="n"/>
-      <c r="G84" s="9" t="n"/>
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="11" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="11" t="n">
+      <c r="A85" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="11" t="n"/>
-      <c r="C85" s="11" t="n"/>
+      <c r="B85" s="12" t="n"/>
+      <c r="C85" s="12" t="n"/>
       <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
-      <c r="F85" s="11" t="n"/>
-      <c r="G85" s="11" t="n"/>
+      <c r="F85" s="12" t="n"/>
+      <c r="G85" s="12" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="n">
+      <c r="A86" s="10" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="9" t="n"/>
-      <c r="C86" s="9" t="n"/>
-      <c r="D86" s="10" t="n"/>
-      <c r="E86" s="10" t="n"/>
-      <c r="F86" s="9" t="n"/>
-      <c r="G86" s="9" t="n"/>
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="11" t="n"/>
+      <c r="E86" s="11" t="n"/>
+      <c r="F86" s="10" t="n"/>
+      <c r="G86" s="10" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="11" t="n">
+      <c r="A87" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="11" t="n"/>
-      <c r="C87" s="11" t="n"/>
+      <c r="B87" s="12" t="n"/>
+      <c r="C87" s="12" t="n"/>
       <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
-      <c r="F87" s="11" t="n"/>
-      <c r="G87" s="11" t="n"/>
+      <c r="F87" s="12" t="n"/>
+      <c r="G87" s="12" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="n">
+      <c r="A88" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="9" t="n"/>
-      <c r="C88" s="9" t="n"/>
-      <c r="D88" s="10" t="n"/>
-      <c r="E88" s="10" t="n"/>
-      <c r="F88" s="9" t="n"/>
-      <c r="G88" s="9" t="n"/>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="11" t="n"/>
+      <c r="E88" s="11" t="n"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="11" t="n">
+      <c r="A89" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="11" t="n"/>
-      <c r="C89" s="11" t="n"/>
+      <c r="B89" s="12" t="n"/>
+      <c r="C89" s="12" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="11" t="n"/>
-      <c r="G89" s="11" t="n"/>
+      <c r="F89" s="12" t="n"/>
+      <c r="G89" s="12" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="n">
+      <c r="A90" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="9" t="n"/>
-      <c r="C90" s="9" t="n"/>
-      <c r="D90" s="10" t="n"/>
-      <c r="E90" s="10" t="n"/>
-      <c r="F90" s="9" t="n"/>
-      <c r="G90" s="9" t="n"/>
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="11" t="n"/>
+      <c r="E90" s="11" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="11" t="n">
+      <c r="A91" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="11" t="n"/>
-      <c r="C91" s="11" t="n"/>
+      <c r="B91" s="12" t="n"/>
+      <c r="C91" s="12" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="11" t="n"/>
-      <c r="G91" s="11" t="n"/>
+      <c r="F91" s="12" t="n"/>
+      <c r="G91" s="12" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="n">
+      <c r="A92" s="10" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="9" t="n"/>
-      <c r="C92" s="9" t="n"/>
-      <c r="D92" s="10" t="n"/>
-      <c r="E92" s="10" t="n"/>
-      <c r="F92" s="9" t="n"/>
-      <c r="G92" s="9" t="n"/>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="11" t="n"/>
+      <c r="E92" s="11" t="n"/>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="10" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="n">
+      <c r="A93" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="11" t="n"/>
-      <c r="C93" s="11" t="n"/>
+      <c r="B93" s="12" t="n"/>
+      <c r="C93" s="12" t="n"/>
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="11" t="n"/>
-      <c r="G93" s="11" t="n"/>
+      <c r="F93" s="12" t="n"/>
+      <c r="G93" s="12" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="n">
+      <c r="A94" s="10" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="9" t="n"/>
-      <c r="C94" s="9" t="n"/>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="9" t="n"/>
-      <c r="G94" s="9" t="n"/>
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="11" t="n"/>
+      <c r="E94" s="11" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="n">
+      <c r="A95" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="11" t="n"/>
-      <c r="C95" s="11" t="n"/>
+      <c r="B95" s="12" t="n"/>
+      <c r="C95" s="12" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="11" t="n"/>
-      <c r="G95" s="11" t="n"/>
+      <c r="F95" s="12" t="n"/>
+      <c r="G95" s="12" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="n">
+      <c r="A96" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="9" t="n"/>
-      <c r="C96" s="9" t="n"/>
-      <c r="D96" s="10" t="n"/>
-      <c r="E96" s="10" t="n"/>
-      <c r="F96" s="9" t="n"/>
-      <c r="G96" s="9" t="n"/>
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="11" t="n"/>
+      <c r="E96" s="11" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="11" t="n">
+      <c r="A97" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="11" t="n"/>
-      <c r="C97" s="11" t="n"/>
+      <c r="B97" s="12" t="n"/>
+      <c r="C97" s="12" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
-      <c r="F97" s="11" t="n"/>
-      <c r="G97" s="11" t="n"/>
+      <c r="F97" s="12" t="n"/>
+      <c r="G97" s="12" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="n">
+      <c r="A98" s="10" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="9" t="n"/>
-      <c r="C98" s="9" t="n"/>
-      <c r="D98" s="10" t="n"/>
-      <c r="E98" s="10" t="n"/>
-      <c r="F98" s="9" t="n"/>
-      <c r="G98" s="9" t="n"/>
+      <c r="B98" s="10" t="n"/>
+      <c r="C98" s="10" t="n"/>
+      <c r="D98" s="11" t="n"/>
+      <c r="E98" s="11" t="n"/>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="10" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="11" t="n">
+      <c r="A99" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="11" t="n"/>
-      <c r="C99" s="11" t="n"/>
+      <c r="B99" s="12" t="n"/>
+      <c r="C99" s="12" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
-      <c r="F99" s="11" t="n"/>
-      <c r="G99" s="11" t="n"/>
+      <c r="F99" s="12" t="n"/>
+      <c r="G99" s="12" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="n">
+      <c r="A100" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="9" t="n"/>
-      <c r="C100" s="9" t="n"/>
-      <c r="D100" s="10" t="n"/>
-      <c r="E100" s="10" t="n"/>
-      <c r="F100" s="9" t="n"/>
-      <c r="G100" s="9" t="n"/>
+      <c r="B100" s="10" t="n"/>
+      <c r="C100" s="10" t="n"/>
+      <c r="D100" s="11" t="n"/>
+      <c r="E100" s="11" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="11" t="n">
+      <c r="A101" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="11" t="n"/>
-      <c r="C101" s="11" t="n"/>
+      <c r="B101" s="12" t="n"/>
+      <c r="C101" s="12" t="n"/>
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
-      <c r="F101" s="11" t="n"/>
-      <c r="G101" s="11" t="n"/>
+      <c r="F101" s="12" t="n"/>
+      <c r="G101" s="12" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="9" t="n">
+      <c r="A102" s="10" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="9" t="n"/>
-      <c r="C102" s="9" t="n"/>
-      <c r="D102" s="10" t="n"/>
-      <c r="E102" s="10" t="n"/>
-      <c r="F102" s="9" t="n"/>
-      <c r="G102" s="9" t="n"/>
+      <c r="B102" s="10" t="n"/>
+      <c r="C102" s="10" t="n"/>
+      <c r="D102" s="11" t="n"/>
+      <c r="E102" s="11" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="n">
+      <c r="A103" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="11" t="n"/>
-      <c r="C103" s="11" t="n"/>
+      <c r="B103" s="12" t="n"/>
+      <c r="C103" s="12" t="n"/>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="11" t="n"/>
-      <c r="G103" s="11" t="n"/>
+      <c r="F103" s="12" t="n"/>
+      <c r="G103" s="12" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="n">
+      <c r="A104" s="10" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="9" t="n"/>
-      <c r="C104" s="9" t="n"/>
-      <c r="D104" s="10" t="n"/>
-      <c r="E104" s="10" t="n"/>
-      <c r="F104" s="9" t="n"/>
-      <c r="G104" s="9" t="n"/>
+      <c r="B104" s="10" t="n"/>
+      <c r="C104" s="10" t="n"/>
+      <c r="D104" s="11" t="n"/>
+      <c r="E104" s="11" t="n"/>
+      <c r="F104" s="10" t="n"/>
+      <c r="G104" s="10" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="11" t="n">
+      <c r="A105" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="11" t="n"/>
-      <c r="C105" s="11" t="n"/>
+      <c r="B105" s="12" t="n"/>
+      <c r="C105" s="12" t="n"/>
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
-      <c r="F105" s="11" t="n"/>
-      <c r="G105" s="11" t="n"/>
+      <c r="F105" s="12" t="n"/>
+      <c r="G105" s="12" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="n">
+      <c r="A106" s="10" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="9" t="n"/>
-      <c r="C106" s="9" t="n"/>
-      <c r="D106" s="10" t="n"/>
-      <c r="E106" s="10" t="n"/>
-      <c r="F106" s="9" t="n"/>
-      <c r="G106" s="9" t="n"/>
+      <c r="B106" s="10" t="n"/>
+      <c r="C106" s="10" t="n"/>
+      <c r="D106" s="11" t="n"/>
+      <c r="E106" s="11" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="n">
+      <c r="A107" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="11" t="n"/>
-      <c r="C107" s="11" t="n"/>
+      <c r="B107" s="12" t="n"/>
+      <c r="C107" s="12" t="n"/>
       <c r="D107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
-      <c r="F107" s="11" t="n"/>
-      <c r="G107" s="11" t="n"/>
+      <c r="F107" s="12" t="n"/>
+      <c r="G107" s="12" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="n">
+      <c r="A108" s="10" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="9" t="n"/>
-      <c r="C108" s="9" t="n"/>
-      <c r="D108" s="10" t="n"/>
-      <c r="E108" s="10" t="n"/>
-      <c r="F108" s="9" t="n"/>
-      <c r="G108" s="9" t="n"/>
+      <c r="B108" s="10" t="n"/>
+      <c r="C108" s="10" t="n"/>
+      <c r="D108" s="11" t="n"/>
+      <c r="E108" s="11" t="n"/>
+      <c r="F108" s="10" t="n"/>
+      <c r="G108" s="10" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="n">
+      <c r="A109" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="11" t="n"/>
-      <c r="C109" s="11" t="n"/>
+      <c r="B109" s="12" t="n"/>
+      <c r="C109" s="12" t="n"/>
       <c r="D109" s="7" t="n"/>
       <c r="E109" s="7" t="n"/>
-      <c r="F109" s="11" t="n"/>
-      <c r="G109" s="11" t="n"/>
+      <c r="F109" s="12" t="n"/>
+      <c r="G109" s="12" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="n">
+      <c r="A110" s="10" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="9" t="n"/>
-      <c r="C110" s="9" t="n"/>
-      <c r="D110" s="10" t="n"/>
-      <c r="E110" s="10" t="n"/>
-      <c r="F110" s="9" t="n"/>
-      <c r="G110" s="9" t="n"/>
+      <c r="B110" s="10" t="n"/>
+      <c r="C110" s="10" t="n"/>
+      <c r="D110" s="11" t="n"/>
+      <c r="E110" s="11" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="11" t="n">
+      <c r="A111" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="11" t="n"/>
-      <c r="C111" s="11" t="n"/>
+      <c r="B111" s="12" t="n"/>
+      <c r="C111" s="12" t="n"/>
       <c r="D111" s="7" t="n"/>
       <c r="E111" s="7" t="n"/>
-      <c r="F111" s="11" t="n"/>
-      <c r="G111" s="11" t="n"/>
+      <c r="F111" s="12" t="n"/>
+      <c r="G111" s="12" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="n">
+      <c r="A112" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="9" t="n"/>
-      <c r="C112" s="9" t="n"/>
-      <c r="D112" s="10" t="n"/>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="9" t="n"/>
-      <c r="G112" s="9" t="n"/>
+      <c r="B112" s="10" t="n"/>
+      <c r="C112" s="10" t="n"/>
+      <c r="D112" s="11" t="n"/>
+      <c r="E112" s="11" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="11" t="n">
+      <c r="A113" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="11" t="n"/>
-      <c r="C113" s="11" t="n"/>
+      <c r="B113" s="12" t="n"/>
+      <c r="C113" s="12" t="n"/>
       <c r="D113" s="7" t="n"/>
       <c r="E113" s="7" t="n"/>
-      <c r="F113" s="11" t="n"/>
-      <c r="G113" s="11" t="n"/>
+      <c r="F113" s="12" t="n"/>
+      <c r="G113" s="12" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="n">
+      <c r="A114" s="10" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="9" t="n"/>
-      <c r="C114" s="9" t="n"/>
-      <c r="D114" s="10" t="n"/>
-      <c r="E114" s="10" t="n"/>
-      <c r="F114" s="9" t="n"/>
-      <c r="G114" s="9" t="n"/>
+      <c r="B114" s="10" t="n"/>
+      <c r="C114" s="10" t="n"/>
+      <c r="D114" s="11" t="n"/>
+      <c r="E114" s="11" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="11" t="n">
+      <c r="A115" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="11" t="n"/>
-      <c r="C115" s="11" t="n"/>
+      <c r="B115" s="12" t="n"/>
+      <c r="C115" s="12" t="n"/>
       <c r="D115" s="7" t="n"/>
       <c r="E115" s="7" t="n"/>
-      <c r="F115" s="11" t="n"/>
-      <c r="G115" s="11" t="n"/>
+      <c r="F115" s="12" t="n"/>
+      <c r="G115" s="12" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="n">
+      <c r="A116" s="10" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="9" t="n"/>
-      <c r="C116" s="9" t="n"/>
-      <c r="D116" s="10" t="n"/>
-      <c r="E116" s="10" t="n"/>
-      <c r="F116" s="9" t="n"/>
-      <c r="G116" s="9" t="n"/>
+      <c r="B116" s="10" t="n"/>
+      <c r="C116" s="10" t="n"/>
+      <c r="D116" s="11" t="n"/>
+      <c r="E116" s="11" t="n"/>
+      <c r="F116" s="10" t="n"/>
+      <c r="G116" s="10" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="11" t="n">
+      <c r="A117" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="11" t="n"/>
-      <c r="C117" s="11" t="n"/>
+      <c r="B117" s="12" t="n"/>
+      <c r="C117" s="12" t="n"/>
       <c r="D117" s="7" t="n"/>
       <c r="E117" s="7" t="n"/>
-      <c r="F117" s="11" t="n"/>
-      <c r="G117" s="11" t="n"/>
+      <c r="F117" s="12" t="n"/>
+      <c r="G117" s="12" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="9" t="n">
+      <c r="A118" s="10" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="9" t="n"/>
-      <c r="C118" s="9" t="n"/>
-      <c r="D118" s="10" t="n"/>
-      <c r="E118" s="10" t="n"/>
-      <c r="F118" s="9" t="n"/>
-      <c r="G118" s="9" t="n"/>
+      <c r="B118" s="10" t="n"/>
+      <c r="C118" s="10" t="n"/>
+      <c r="D118" s="11" t="n"/>
+      <c r="E118" s="11" t="n"/>
+      <c r="F118" s="10" t="n"/>
+      <c r="G118" s="10" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="11" t="n">
+      <c r="A119" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="11" t="n"/>
-      <c r="C119" s="11" t="n"/>
+      <c r="B119" s="12" t="n"/>
+      <c r="C119" s="12" t="n"/>
       <c r="D119" s="7" t="n"/>
       <c r="E119" s="7" t="n"/>
-      <c r="F119" s="11" t="n"/>
-      <c r="G119" s="11" t="n"/>
+      <c r="F119" s="12" t="n"/>
+      <c r="G119" s="12" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="n">
+      <c r="A120" s="10" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="9" t="n"/>
-      <c r="C120" s="9" t="n"/>
-      <c r="D120" s="10" t="n"/>
-      <c r="E120" s="10" t="n"/>
-      <c r="F120" s="9" t="n"/>
-      <c r="G120" s="9" t="n"/>
+      <c r="B120" s="10" t="n"/>
+      <c r="C120" s="10" t="n"/>
+      <c r="D120" s="11" t="n"/>
+      <c r="E120" s="11" t="n"/>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -2522,12 +2530,12 @@
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>3번 항목</t>
         </is>
@@ -2540,15 +2548,15 @@
 → ②라면 블로그와 링크드인 주소를 알려주세요.</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr"/>
+      <c r="D2" s="15" t="inlineStr"/>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>5번 항목</t>
         </is>
@@ -2559,15 +2567,15 @@
 보내주신 문서에 물음표가 붙어 있어 확인드립니다. 다른 후보가 있으면 함께 알려주세요.</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr"/>
+      <c r="D3" s="15" t="inlineStr"/>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>8번 항목</t>
         </is>
@@ -2578,15 +2586,15 @@
 예: 누적 출원 건수, 자문 기업 수, 상담 회신 시간 등.</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr"/>
+      <c r="D4" s="15" t="inlineStr"/>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>15번 항목</t>
         </is>
@@ -2597,15 +2605,15 @@
 ① 의료소송 수행 목록  ② 자문 목록  ③ 출원 목록(수술도구·슬리퍼 등)</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr"/>
+      <c r="D5" s="15" t="inlineStr"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>16번 항목</t>
         </is>
@@ -2616,15 +2624,15 @@
 책 제목과 함께, 책별로 무료배포 링크 또는 구매 페이지 주소를 알려주세요.</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr"/>
+      <c r="D6" s="15" t="inlineStr"/>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>18번 항목</t>
         </is>
@@ -2636,15 +2644,15 @@
 부가세 별도 여부도 알려주세요.</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr"/>
+      <c r="D7" s="15" t="inlineStr"/>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Q7</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>20번 항목</t>
         </is>
@@ -2655,7 +2663,7 @@
 (예: 소개 페이지의 참고 자료로 소개 / 반영하지 않음)</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr"/>
+      <c r="D8" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3013,189 +3021,189 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>02-1234-5678 (임시)</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr"/>
+      <c r="C2" s="18" t="inlineStr"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>이메일</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>contact@example.com (임시)</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr"/>
+      <c r="C3" s="18" t="inlineStr"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>서울특별시 서초구 반포대로 00, 0층 (임시)</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr"/>
+      <c r="C4" s="18" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>상담 가능 시간</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>평일 09:00–18:00, 점심 12:00–13:00 (임시)</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr"/>
+      <c r="C5" s="18" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>카카오톡 채널 주소</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>임시 링크</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr"/>
+      <c r="C6" s="18" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>실적 수치 ① 누적 출원·등록</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>3,200+ (예시)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr"/>
+      <c r="C7" s="18" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>실적 수치 ② 상표 등록 성공률</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>98% (예시)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr"/>
+      <c r="C8" s="18" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>실적 수치 ③ 실무 경력</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>15년+ (예시)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>실적 수치 ④ 상담 회신</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>24시간 이내 (예시)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr"/>
+      <c r="C10" s="18" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>로고 파일</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>없음 — 글자 '오'로 임시 표시</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr"/>
+      <c r="C11" s="18" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>대표 프로필 사진</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>없음 — 회색 박스로 임시 표시</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr"/>
+      <c r="C12" s="18" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>지도 사용 여부</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>빈 박스</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr"/>
+      <c r="C13" s="18" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>상담 신청 접수 방법</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr"/>
+      <c r="C14" s="18" t="inlineStr"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>사이트 주소(도메인)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr"/>
+      <c r="C15" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>※ 로고 파일과 대표 사진은 파일을 메일·카톡으로 함께 보내 주세요. (PNG/JPG, 가능한 원본 크기)</t>
         </is>

--- a/clients/yeri/feedback/피드백-작성-양식.xlsx
+++ b/clients/yeri/feedback/피드백-작성-양식.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>사이트 색상 테마를 바꿉니다. 지금의 남색+금색 조합 대신 → 배경은 흰색 유지, 주요 색은 차콜 그레이(#2D3748), 포인트 색은 연한 피치 핑크(#E5A99E). 젊은 뷰티·디자인 분야 고객이 타겟이라 트렌디한 분위기를 원함 (참고 사이트와 같은 느낌).</t>
+          <t>사이트 색상을 바꿔 주세요. 지금의 남색과 금색 조합 대신, 배경은 흰색을 유지하고 주요 색은 차콜 그레이(#2D3748), 포인트 색은 연한 피치 핑크(#E5A99E)로 해주세요. 주 고객이 젊은 뷰티·디자인 분야라서 트렌디한 분위기를 원합니다.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>상단 메뉴에 두 가지를 추가합니다: ① LinkedIn 바로가기 ② 언어 전환 버튼(한/영/중). 기존 메뉴 4개(홈·소개·서비스·상담)는 그대로 둡니다.</t>
+          <t>상단 메뉴에 LinkedIn 바로가기와 언어 전환 버튼(한/영/중)을 추가해 주세요. 기존 메뉴 네 개(홈·소개·서비스·상담)는 그대로 둡니다.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -799,7 +799,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>언어 버튼(한/영/중)을 눌렀을 때의 동작이 불분명합니다. 번역된 페이지로 바뀌는 게 아니라 외부 채널로 이동하는 것으로 보임 (원문: '한국어클릭은 블로그연동/ 중한은 링크드인연동'). 어느 언어가 어디로 연결되는지, 블로그·링크드인 주소가 무엇인지 답변을 기다리는 중.</t>
+          <t>언어 버튼(한/영/중)을 눌렀을 때 무엇이 되어야 하는지 정해야 합니다. 고객 설명으로는 페이지가 번역되는 것이 아니라 한국어 버튼은 블로그로, 중국어 버튼은 링크드인으로 연결되는 것으로 보입니다. 어느 버튼이 어디로 연결되는지, 블로그와 링크드인 주소는 무엇인지 고객 답변을 기다리고 있습니다.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>지금 사이트의 뼈대(페이지 구성)는 유지하되, 참고 사이트들(유레카 특허법률사무소 등)에 있는 콘텐츠 요소들을 참고해서 내용을 더 풍부하게 보강해 달라는 요청.</t>
+          <t>페이지 구성은 지금 그대로 두고, 내용을 더 풍부하게 채워 주세요. 유레카 특허법률사무소 같은 다른 특허사무소 사이트에 있는 콘텐츠 요소들을 참고하면 됩니다.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>메인 배너 제목 후보로 '꿈을 현실로 만들어 드립니다'가 제시됨. 다만 원문에 물음표가 붙어 있어 확정 문구인지 답변을 기다리는 중.</t>
+          <t>메인 배너 제목을 '꿈을 현실로 만들어 드립니다'로 바꾸자는 의견이 있었습니다. 다만 고객이 물음표를 붙여 보낸 문구라 확정인지 아닌지 답변을 기다리고 있습니다.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>메인 배너 근처에 이 사무소만의 차별점 3가지를 보여줍니다: ① 출원부터 법률자문·소송·투자유치 자료까지 변호사+변리사가 1:1 전담 ② 의료·뷰티·디자인 분야 전문성 ③ 영어·중국어 상담 가능.</t>
+          <t>메인 배너 근처에 이 사무소만의 강점 세 가지를 보여 주세요. 첫째, 출원부터 법률자문·소송·투자유치 자료까지 변호사 겸 변리사가 1:1 전담. 둘째, 의료·뷰티·디자인 분야 전문성. 셋째, 영어·중국어 상담 가능.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
@@ -935,7 +935,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>사이트 전체에서 '무료 상담' 표현을 없애고 '상담 신청'으로 바꿉니다. 이유: 상담이 유료로 바뀌기 때문 (19번 상담 정책 변경과 한 세트).</t>
+          <t>사이트 곳곳의 '무료 상담'이라는 표현을 전부 '상담 신청'으로 바꿔 주세요. 상담이 유료로 바뀌기 때문입니다.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>실적 수치 4칸의 디자인(칸 구성)은 유지하고 내용만 바꿉니다: ① 전문성 → '의료 &amp; IP 전략' ② 소통 → '영어·중국어 가능' ③ 실무 경력 → '9년+' ④ 네 번째 칸은 내용 미정 (원문: '칸 남겨줘') — 답변을 기다리는 중.</t>
+          <t>실적 수치 네 칸은 모양은 그대로 두고 내용만 바꿔 주세요. '전문성' 칸은 '의료 &amp; IP 전략'으로, '소통' 칸은 '영어·중국어 가능'으로, '실무 경력' 칸은 '9년+'로. 네 번째 칸에 무엇을 넣을지는 아직 정해지지 않아 고객 답변을 기다리고 있습니다.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>업무 분야 카드 6개의 제목·설명 문구를 새 서비스 구성(17번 재편안)에 맞게 바꿉니다. 카드가 6개인 것은 그대로 유지.</t>
+          <t>업무 분야 카드 여섯 개의 제목과 설명을, 새로 짜는 서비스 여섯 분야 구성에 맞춰 바꿔 주세요. 카드가 여섯 개인 것은 그대로 유지합니다.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>진행 절차 5단계 구성은 그대로 두고, '무료 상담 접수' 등 비용이 언급되는 문구만 유료 정책(19번)에 맞게 고칩니다.</t>
+          <t>진행 절차 다섯 단계 구성은 그대로 두고, '무료 상담 접수'처럼 비용이 언급되는 문구만 상담 유료화에 맞게 고쳐 주세요.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>FAQ 6개 구성은 그대로 두고, '상담은 정말 무료인가요?' 등 비용 관련 답변만 유료 정책(19번)에 맞게 고칩니다.</t>
+          <t>FAQ 여섯 개 구성은 그대로 두고, '상담은 정말 무료인가요?' 같은 비용 관련 답변만 상담 유료화에 맞게 고쳐 주세요.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>연락 수단에서 전화를 뺍니다. 카카오톡 상담과 게시판(상담 폼) 두 가지만 남기고, 헤더·푸터·플로팅 버튼 등 전화번호가 보이는 곳을 전부 정리합니다.</t>
+          <t>연락 수단에서 전화를 빼 주세요. 카카오톡 상담과 상담 신청 폼 두 가지만 남기고, 헤더·푸터·플로팅 버튼처럼 전화번호가 보이는 곳을 전부 정리합니다.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>홈에 협력·관련 기관 로고를 나열하는 섹션을 새로 만듭니다: 특허청, 키프리스, 한국발명진흥회, 특허심판원, 특허법원, 칭화대. (칭화대 로고 이미지는 feedback 폴더에 첨부되어 있음)</t>
+          <t>홈에 협력·관련 기관의 로고를 나열하는 섹션을 새로 만들어 주세요. 들어갈 기관은 특허청, 키프리스, 한국발명진흥회, 특허심판원, 특허법원, 칭화대이고 칭화대 로고 이미지는 받아 둔 상태입니다.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>대표 직함을 '오예리 대표 변호사·변리사'로 바꿉니다 (변호사 자격 추가). 영문 표기는 'dual-qualified Attorney-at-Law &amp; Patent Attorney (Korea)'.</t>
+          <t>대표 직함을 '오예리 대표 변호사·변리사'로 바꿔 주세요 (변호사 자격 추가). 영문으로는 'dual-qualified Attorney-at-Law &amp; Patent Attorney (Korea)'로 표기합니다.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>대표 프로필에 전문분야 '의료 &amp; IP 전략' 소개를 추가합니다. [의료] 20년차 신경외과·영상의학과 전문의 자문 경력, 의료소송·자문 사례 목록 / [IP 전략] 중국 IP 금융 자문, 출원 사례(수술도구·슬리퍼 등) 목록. 사례 목록 자료는 고객이 보내줘야 함 — 답변을 기다리는 중.</t>
+          <t>대표 프로필에 전문분야 '의료 &amp; IP 전략' 소개를 추가해 주세요. 의료 쪽은 20년차 신경외과·영상의학과 전문의 자문 경력과 의료소송·자문 사례 목록을, IP 전략 쪽은 중국 IP 금융 자문 경력과 수술도구·슬리퍼 등 출원 사례 목록을 싣습니다. 사례 목록 자료는 고객이 보내 주셔야 해서 기다리고 있습니다.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>소개 페이지에 대표 저서 소개 섹션을 새로 만듭니다. 책 표지를 클릭하면 무료배포 페이지 또는 구매 페이지로 이동. 표지 이미지는 받았지만 연결할 주소가 없음 — 답변을 기다리는 중.</t>
+          <t>소개 페이지에 대표님 저서를 소개하는 섹션을 새로 만들어 주세요. 책 표지를 클릭하면 무료배포 페이지나 구매 페이지로 이동합니다. 표지 이미지는 받았지만 연결할 주소가 아직 없어 답변을 기다리고 있습니다.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>서비스 6개 분야를 완전히 새로 짭니다. 지금: 특허/상표/디자인/심판/소송/해외출원 → 새 구성: ① IP 등록 (특허·상표·디자인·저작권 — 비용과 절차를 명시) ② 해외출원 ③ 조사 (선행기술조사 / 기술가치평가·기술이전·라이선스 컨설팅 / 시장조사) ④ 전략 (특허맵, IP-R&amp;D 컨설팅, IP 포트폴리오 설계 — 국내외 진출·투자유치 지원) ⑤ 침해 대응·민형사 소송 (경고장, 가처분, 병행수입·통관보류 분쟁, 권리범위확인심판 등) ⑥ 영업비밀·부정경쟁행위 (전직금지가처분, 비밀유지계약서 작성 등)</t>
+          <t>서비스 여섯 분야를 완전히 새로 짭니다. 지금의 특허/상표/디자인/심판/소송/해외출원 대신 이렇게 바꿔 주세요. 1) IP 등록: 특허·상표·디자인·저작권, 비용과 절차를 명시. 2) 해외출원. 3) 조사: 선행기술조사, 기술가치평가·기술이전·라이선스 컨설팅, 시장조사. 4) 전략: 특허맵, IP-R&amp;D 컨설팅, IP 포트폴리오 설계로 국내외 진출과 투자유치를 지원. 5) 침해 대응과 민형사 소송: 경고장, 가처분, 병행수입·통관보류 분쟁, 권리범위확인심판 등. 6) 영업비밀과 부정경쟁행위: 전직금지가처분, 비밀유지계약서 작성 등.</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>등록 비용을 사이트에 표기합니다. 고객이 준 수치: 특허 140 / 상표는 빠른 심사 20+20, 기본 6+12 / 디자인 30+30 / 저작권 30. 단위가 만원인지, 두 숫자가 착수금+등록료인지 불분명 — 답변을 기다리는 중.</t>
+          <t>등록 비용을 사이트에 표기해 주세요. 고객이 준 수치는 특허 140, 상표는 빠른 심사 20+20 또는 기본 6+12, 디자인 30+30, 저작권 30입니다. 단위가 만원인지, 두 숫자가 착수금과 등록료를 뜻하는지 불분명해 고객 답변을 기다리고 있습니다.</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>상담 정책을 바꿉니다: 무료 상담 → 기본 30분 5만원(변호사법 근거), 복잡한 사안은 시간당 과금. 상담 페이지·하단 배너·FAQ 등 '무료'라고 안내하던 곳을 전부 새 정책으로 교체.</t>
+          <t>상담을 유료로 바꿉니다. 기본 30분에 5만원(변호사법 근거)이고 복잡한 사안은 시간당 과금입니다. 상담 페이지·하단 배너·FAQ처럼 '무료'라고 안내하던 곳을 전부 새 정책으로 교체해 주세요.</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>받은 문서에 WIPO(세계지식재산기구) 교육과정 소개 글이 들어 있는데, 사이트에 쓰라는 건지 단순 참고용인지 알 수 없음 — 용도 답변을 기다리는 중.</t>
+          <t>받은 문서에 WIPO(세계지식재산기구) 교육과정을 소개하는 글이 들어 있었습니다. 사이트에 실으라는 것인지 단순 참고용인지 알 수 없어 용도를 여쭤보고 있습니다.</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">

--- a/clients/yeri/feedback/피드백-작성-양식.xlsx
+++ b/clients/yeri/feedback/피드백-작성-양식.xlsx
@@ -913,9 +913,9 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>

--- a/clients/yeri/feedback/피드백-작성-양식.xlsx
+++ b/clients/yeri/feedback/피드백-작성-양식.xlsx
@@ -944,9 +944,9 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -1011,9 +1011,9 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -1042,9 +1042,9 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -1073,9 +1073,9 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -1104,9 +1104,9 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -1139,9 +1139,9 @@
           <t>B (가능하면)</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -1170,9 +1170,9 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -1276,9 +1276,9 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -1342,9 +1342,9 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>

--- a/clients/yeri/feedback/피드백-작성-양식.xlsx
+++ b/clients/yeri/feedback/피드백-작성-양식.xlsx
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +78,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -122,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -152,9 +157,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -166,7 +174,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -175,7 +183,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -777,9 +785,9 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>대기</t>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -812,7 +820,7 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
@@ -882,7 +890,7 @@
           <t>B (가능하면)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
@@ -980,7 +988,7 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
@@ -1207,7 +1215,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>확인 필요 (고객 답변 대기)</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1251,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>확인 필요 (고객 답변 대기)</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1319,7 @@
           <t>A (오픈 전 꼭)</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
@@ -1378,1100 +1386,1100 @@
           <t>C (아이디어)</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>확인 필요 (고객 답변 대기)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n">
+      <c r="A27" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n">
+      <c r="A29" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="13" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="A31" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="13" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n">
+      <c r="A33" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="13" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="13" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="11" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="13" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="n">
+      <c r="A37" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="13" t="n"/>
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="13" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n">
+      <c r="A38" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="10" t="n"/>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="n">
+      <c r="A39" s="13" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="13" t="n"/>
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="12" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="11" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="n">
+      <c r="A41" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="13" t="n"/>
       <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="13" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n">
+      <c r="A42" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="n">
+      <c r="A43" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="13" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="13" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n">
+      <c r="A44" s="11" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="n">
+      <c r="A45" s="13" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
+      <c r="B45" s="13" t="n"/>
+      <c r="C45" s="13" t="n"/>
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
-      <c r="F45" s="12" t="n"/>
-      <c r="G45" s="12" t="n"/>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="13" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="n">
+      <c r="A46" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="12" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="11" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="n">
+      <c r="A47" s="13" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="13" t="n"/>
       <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
-      <c r="F47" s="12" t="n"/>
-      <c r="G47" s="12" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="13" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="n">
+      <c r="A48" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="10" t="n"/>
-      <c r="G48" s="10" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="12" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="11" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="n">
+      <c r="A49" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
+      <c r="B49" s="13" t="n"/>
+      <c r="C49" s="13" t="n"/>
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
-      <c r="F49" s="12" t="n"/>
-      <c r="G49" s="12" t="n"/>
+      <c r="F49" s="13" t="n"/>
+      <c r="G49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n">
+      <c r="A50" s="11" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="11" t="n"/>
-      <c r="E50" s="11" t="n"/>
-      <c r="F50" s="10" t="n"/>
-      <c r="G50" s="10" t="n"/>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="11" t="n"/>
+      <c r="G50" s="11" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="n">
+      <c r="A51" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
+      <c r="B51" s="13" t="n"/>
+      <c r="C51" s="13" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="12" t="n"/>
-      <c r="G51" s="12" t="n"/>
+      <c r="F51" s="13" t="n"/>
+      <c r="G51" s="13" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="n">
+      <c r="A52" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="11" t="n"/>
-      <c r="E52" s="11" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="11" t="n"/>
+      <c r="G52" s="11" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="n">
+      <c r="A53" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="12" t="n"/>
-      <c r="C53" s="12" t="n"/>
+      <c r="B53" s="13" t="n"/>
+      <c r="C53" s="13" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="12" t="n"/>
-      <c r="G53" s="12" t="n"/>
+      <c r="F53" s="13" t="n"/>
+      <c r="G53" s="13" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="n">
+      <c r="A54" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="10" t="n"/>
-      <c r="D54" s="11" t="n"/>
-      <c r="E54" s="11" t="n"/>
-      <c r="F54" s="10" t="n"/>
-      <c r="G54" s="10" t="n"/>
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="12" t="n"/>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="11" t="n"/>
+      <c r="G54" s="11" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="n">
+      <c r="A55" s="13" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
+      <c r="B55" s="13" t="n"/>
+      <c r="C55" s="13" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="12" t="n"/>
-      <c r="G55" s="12" t="n"/>
+      <c r="F55" s="13" t="n"/>
+      <c r="G55" s="13" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="n">
+      <c r="A56" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="10" t="n"/>
-      <c r="C56" s="10" t="n"/>
-      <c r="D56" s="11" t="n"/>
-      <c r="E56" s="11" t="n"/>
-      <c r="F56" s="10" t="n"/>
-      <c r="G56" s="10" t="n"/>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="12" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="11" t="n"/>
+      <c r="G56" s="11" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="n">
+      <c r="A57" s="13" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="12" t="n"/>
-      <c r="C57" s="12" t="n"/>
+      <c r="B57" s="13" t="n"/>
+      <c r="C57" s="13" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="12" t="n"/>
-      <c r="G57" s="12" t="n"/>
+      <c r="F57" s="13" t="n"/>
+      <c r="G57" s="13" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n">
+      <c r="A58" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="11" t="n"/>
-      <c r="E58" s="11" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
+      <c r="B58" s="11" t="n"/>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="12" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="11" t="n"/>
+      <c r="G58" s="11" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="n">
+      <c r="A59" s="13" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
+      <c r="B59" s="13" t="n"/>
+      <c r="C59" s="13" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="12" t="n"/>
-      <c r="G59" s="12" t="n"/>
+      <c r="F59" s="13" t="n"/>
+      <c r="G59" s="13" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="n">
+      <c r="A60" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="10" t="n"/>
-      <c r="C60" s="10" t="n"/>
-      <c r="D60" s="11" t="n"/>
-      <c r="E60" s="11" t="n"/>
-      <c r="F60" s="10" t="n"/>
-      <c r="G60" s="10" t="n"/>
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="12" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="11" t="n"/>
+      <c r="G60" s="11" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="n">
+      <c r="A61" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
+      <c r="B61" s="13" t="n"/>
+      <c r="C61" s="13" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="12" t="n"/>
-      <c r="G61" s="12" t="n"/>
+      <c r="F61" s="13" t="n"/>
+      <c r="G61" s="13" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="n">
+      <c r="A62" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="10" t="n"/>
-      <c r="C62" s="10" t="n"/>
-      <c r="D62" s="11" t="n"/>
-      <c r="E62" s="11" t="n"/>
-      <c r="F62" s="10" t="n"/>
-      <c r="G62" s="10" t="n"/>
+      <c r="B62" s="11" t="n"/>
+      <c r="C62" s="11" t="n"/>
+      <c r="D62" s="12" t="n"/>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="11" t="n"/>
+      <c r="G62" s="11" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="n">
+      <c r="A63" s="13" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="12" t="n"/>
+      <c r="B63" s="13" t="n"/>
+      <c r="C63" s="13" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="12" t="n"/>
-      <c r="G63" s="12" t="n"/>
+      <c r="F63" s="13" t="n"/>
+      <c r="G63" s="13" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="n">
+      <c r="A64" s="11" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="10" t="n"/>
-      <c r="C64" s="10" t="n"/>
-      <c r="D64" s="11" t="n"/>
-      <c r="E64" s="11" t="n"/>
-      <c r="F64" s="10" t="n"/>
-      <c r="G64" s="10" t="n"/>
+      <c r="B64" s="11" t="n"/>
+      <c r="C64" s="11" t="n"/>
+      <c r="D64" s="12" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="11" t="n"/>
+      <c r="G64" s="11" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="n">
+      <c r="A65" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="12" t="n"/>
+      <c r="B65" s="13" t="n"/>
+      <c r="C65" s="13" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="12" t="n"/>
-      <c r="G65" s="12" t="n"/>
+      <c r="F65" s="13" t="n"/>
+      <c r="G65" s="13" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="n">
+      <c r="A66" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="11" t="n"/>
-      <c r="E66" s="11" t="n"/>
-      <c r="F66" s="10" t="n"/>
-      <c r="G66" s="10" t="n"/>
+      <c r="B66" s="11" t="n"/>
+      <c r="C66" s="11" t="n"/>
+      <c r="D66" s="12" t="n"/>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="11" t="n"/>
+      <c r="G66" s="11" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="n">
+      <c r="A67" s="13" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="12" t="n"/>
-      <c r="C67" s="12" t="n"/>
+      <c r="B67" s="13" t="n"/>
+      <c r="C67" s="13" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
-      <c r="F67" s="12" t="n"/>
-      <c r="G67" s="12" t="n"/>
+      <c r="F67" s="13" t="n"/>
+      <c r="G67" s="13" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="n">
+      <c r="A68" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="10" t="n"/>
-      <c r="C68" s="10" t="n"/>
-      <c r="D68" s="11" t="n"/>
-      <c r="E68" s="11" t="n"/>
-      <c r="F68" s="10" t="n"/>
-      <c r="G68" s="10" t="n"/>
+      <c r="B68" s="11" t="n"/>
+      <c r="C68" s="11" t="n"/>
+      <c r="D68" s="12" t="n"/>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="11" t="n"/>
+      <c r="G68" s="11" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="n">
+      <c r="A69" s="13" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
+      <c r="B69" s="13" t="n"/>
+      <c r="C69" s="13" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
-      <c r="F69" s="12" t="n"/>
-      <c r="G69" s="12" t="n"/>
+      <c r="F69" s="13" t="n"/>
+      <c r="G69" s="13" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="n">
+      <c r="A70" s="11" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="10" t="n"/>
-      <c r="D70" s="11" t="n"/>
-      <c r="E70" s="11" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
+      <c r="B70" s="11" t="n"/>
+      <c r="C70" s="11" t="n"/>
+      <c r="D70" s="12" t="n"/>
+      <c r="E70" s="12" t="n"/>
+      <c r="F70" s="11" t="n"/>
+      <c r="G70" s="11" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="12" t="n">
+      <c r="A71" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="12" t="n"/>
-      <c r="C71" s="12" t="n"/>
+      <c r="B71" s="13" t="n"/>
+      <c r="C71" s="13" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
-      <c r="F71" s="12" t="n"/>
-      <c r="G71" s="12" t="n"/>
+      <c r="F71" s="13" t="n"/>
+      <c r="G71" s="13" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="n">
+      <c r="A72" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="10" t="n"/>
-      <c r="D72" s="11" t="n"/>
-      <c r="E72" s="11" t="n"/>
-      <c r="F72" s="10" t="n"/>
-      <c r="G72" s="10" t="n"/>
+      <c r="B72" s="11" t="n"/>
+      <c r="C72" s="11" t="n"/>
+      <c r="D72" s="12" t="n"/>
+      <c r="E72" s="12" t="n"/>
+      <c r="F72" s="11" t="n"/>
+      <c r="G72" s="11" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="12" t="n">
+      <c r="A73" s="13" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="12" t="n"/>
+      <c r="B73" s="13" t="n"/>
+      <c r="C73" s="13" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="12" t="n"/>
-      <c r="G73" s="12" t="n"/>
+      <c r="F73" s="13" t="n"/>
+      <c r="G73" s="13" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="n">
+      <c r="A74" s="11" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="10" t="n"/>
-      <c r="C74" s="10" t="n"/>
-      <c r="D74" s="11" t="n"/>
-      <c r="E74" s="11" t="n"/>
-      <c r="F74" s="10" t="n"/>
-      <c r="G74" s="10" t="n"/>
+      <c r="B74" s="11" t="n"/>
+      <c r="C74" s="11" t="n"/>
+      <c r="D74" s="12" t="n"/>
+      <c r="E74" s="12" t="n"/>
+      <c r="F74" s="11" t="n"/>
+      <c r="G74" s="11" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="12" t="n">
+      <c r="A75" s="13" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="12" t="n"/>
-      <c r="C75" s="12" t="n"/>
+      <c r="B75" s="13" t="n"/>
+      <c r="C75" s="13" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
-      <c r="F75" s="12" t="n"/>
-      <c r="G75" s="12" t="n"/>
+      <c r="F75" s="13" t="n"/>
+      <c r="G75" s="13" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="n">
+      <c r="A76" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="10" t="n"/>
-      <c r="C76" s="10" t="n"/>
-      <c r="D76" s="11" t="n"/>
-      <c r="E76" s="11" t="n"/>
-      <c r="F76" s="10" t="n"/>
-      <c r="G76" s="10" t="n"/>
+      <c r="B76" s="11" t="n"/>
+      <c r="C76" s="11" t="n"/>
+      <c r="D76" s="12" t="n"/>
+      <c r="E76" s="12" t="n"/>
+      <c r="F76" s="11" t="n"/>
+      <c r="G76" s="11" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="12" t="n">
+      <c r="A77" s="13" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="12" t="n"/>
-      <c r="C77" s="12" t="n"/>
+      <c r="B77" s="13" t="n"/>
+      <c r="C77" s="13" t="n"/>
       <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
-      <c r="F77" s="12" t="n"/>
-      <c r="G77" s="12" t="n"/>
+      <c r="F77" s="13" t="n"/>
+      <c r="G77" s="13" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="n">
+      <c r="A78" s="11" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="10" t="n"/>
-      <c r="C78" s="10" t="n"/>
-      <c r="D78" s="11" t="n"/>
-      <c r="E78" s="11" t="n"/>
-      <c r="F78" s="10" t="n"/>
-      <c r="G78" s="10" t="n"/>
+      <c r="B78" s="11" t="n"/>
+      <c r="C78" s="11" t="n"/>
+      <c r="D78" s="12" t="n"/>
+      <c r="E78" s="12" t="n"/>
+      <c r="F78" s="11" t="n"/>
+      <c r="G78" s="11" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="n">
+      <c r="A79" s="13" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="12" t="n"/>
-      <c r="C79" s="12" t="n"/>
+      <c r="B79" s="13" t="n"/>
+      <c r="C79" s="13" t="n"/>
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="12" t="n"/>
-      <c r="G79" s="12" t="n"/>
+      <c r="F79" s="13" t="n"/>
+      <c r="G79" s="13" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="n">
+      <c r="A80" s="11" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="10" t="n"/>
-      <c r="C80" s="10" t="n"/>
-      <c r="D80" s="11" t="n"/>
-      <c r="E80" s="11" t="n"/>
-      <c r="F80" s="10" t="n"/>
-      <c r="G80" s="10" t="n"/>
+      <c r="B80" s="11" t="n"/>
+      <c r="C80" s="11" t="n"/>
+      <c r="D80" s="12" t="n"/>
+      <c r="E80" s="12" t="n"/>
+      <c r="F80" s="11" t="n"/>
+      <c r="G80" s="11" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="n">
+      <c r="A81" s="13" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="12" t="n"/>
+      <c r="B81" s="13" t="n"/>
+      <c r="C81" s="13" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="12" t="n"/>
-      <c r="G81" s="12" t="n"/>
+      <c r="F81" s="13" t="n"/>
+      <c r="G81" s="13" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="n">
+      <c r="A82" s="11" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="10" t="n"/>
-      <c r="C82" s="10" t="n"/>
-      <c r="D82" s="11" t="n"/>
-      <c r="E82" s="11" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
+      <c r="B82" s="11" t="n"/>
+      <c r="C82" s="11" t="n"/>
+      <c r="D82" s="12" t="n"/>
+      <c r="E82" s="12" t="n"/>
+      <c r="F82" s="11" t="n"/>
+      <c r="G82" s="11" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="12" t="n">
+      <c r="A83" s="13" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="12" t="n"/>
-      <c r="C83" s="12" t="n"/>
+      <c r="B83" s="13" t="n"/>
+      <c r="C83" s="13" t="n"/>
       <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
-      <c r="F83" s="12" t="n"/>
-      <c r="G83" s="12" t="n"/>
+      <c r="F83" s="13" t="n"/>
+      <c r="G83" s="13" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="n">
+      <c r="A84" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="10" t="n"/>
-      <c r="C84" s="10" t="n"/>
-      <c r="D84" s="11" t="n"/>
-      <c r="E84" s="11" t="n"/>
-      <c r="F84" s="10" t="n"/>
-      <c r="G84" s="10" t="n"/>
+      <c r="B84" s="11" t="n"/>
+      <c r="C84" s="11" t="n"/>
+      <c r="D84" s="12" t="n"/>
+      <c r="E84" s="12" t="n"/>
+      <c r="F84" s="11" t="n"/>
+      <c r="G84" s="11" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="n">
+      <c r="A85" s="13" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="12" t="n"/>
+      <c r="B85" s="13" t="n"/>
+      <c r="C85" s="13" t="n"/>
       <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
-      <c r="F85" s="12" t="n"/>
-      <c r="G85" s="12" t="n"/>
+      <c r="F85" s="13" t="n"/>
+      <c r="G85" s="13" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="n">
+      <c r="A86" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="10" t="n"/>
-      <c r="C86" s="10" t="n"/>
-      <c r="D86" s="11" t="n"/>
-      <c r="E86" s="11" t="n"/>
-      <c r="F86" s="10" t="n"/>
-      <c r="G86" s="10" t="n"/>
+      <c r="B86" s="11" t="n"/>
+      <c r="C86" s="11" t="n"/>
+      <c r="D86" s="12" t="n"/>
+      <c r="E86" s="12" t="n"/>
+      <c r="F86" s="11" t="n"/>
+      <c r="G86" s="11" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="12" t="n">
+      <c r="A87" s="13" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="12" t="n"/>
-      <c r="C87" s="12" t="n"/>
+      <c r="B87" s="13" t="n"/>
+      <c r="C87" s="13" t="n"/>
       <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
-      <c r="F87" s="12" t="n"/>
-      <c r="G87" s="12" t="n"/>
+      <c r="F87" s="13" t="n"/>
+      <c r="G87" s="13" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="n">
+      <c r="A88" s="11" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="10" t="n"/>
-      <c r="C88" s="10" t="n"/>
-      <c r="D88" s="11" t="n"/>
-      <c r="E88" s="11" t="n"/>
-      <c r="F88" s="10" t="n"/>
-      <c r="G88" s="10" t="n"/>
+      <c r="B88" s="11" t="n"/>
+      <c r="C88" s="11" t="n"/>
+      <c r="D88" s="12" t="n"/>
+      <c r="E88" s="12" t="n"/>
+      <c r="F88" s="11" t="n"/>
+      <c r="G88" s="11" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="12" t="n">
+      <c r="A89" s="13" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="12" t="n"/>
-      <c r="C89" s="12" t="n"/>
+      <c r="B89" s="13" t="n"/>
+      <c r="C89" s="13" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="12" t="n"/>
-      <c r="G89" s="12" t="n"/>
+      <c r="F89" s="13" t="n"/>
+      <c r="G89" s="13" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="n">
+      <c r="A90" s="11" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="10" t="n"/>
-      <c r="C90" s="10" t="n"/>
-      <c r="D90" s="11" t="n"/>
-      <c r="E90" s="11" t="n"/>
-      <c r="F90" s="10" t="n"/>
-      <c r="G90" s="10" t="n"/>
+      <c r="B90" s="11" t="n"/>
+      <c r="C90" s="11" t="n"/>
+      <c r="D90" s="12" t="n"/>
+      <c r="E90" s="12" t="n"/>
+      <c r="F90" s="11" t="n"/>
+      <c r="G90" s="11" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="n">
+      <c r="A91" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="12" t="n"/>
-      <c r="C91" s="12" t="n"/>
+      <c r="B91" s="13" t="n"/>
+      <c r="C91" s="13" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="12" t="n"/>
-      <c r="G91" s="12" t="n"/>
+      <c r="F91" s="13" t="n"/>
+      <c r="G91" s="13" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="n">
+      <c r="A92" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="10" t="n"/>
-      <c r="C92" s="10" t="n"/>
-      <c r="D92" s="11" t="n"/>
-      <c r="E92" s="11" t="n"/>
-      <c r="F92" s="10" t="n"/>
-      <c r="G92" s="10" t="n"/>
+      <c r="B92" s="11" t="n"/>
+      <c r="C92" s="11" t="n"/>
+      <c r="D92" s="12" t="n"/>
+      <c r="E92" s="12" t="n"/>
+      <c r="F92" s="11" t="n"/>
+      <c r="G92" s="11" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="12" t="n">
+      <c r="A93" s="13" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="12" t="n"/>
-      <c r="C93" s="12" t="n"/>
+      <c r="B93" s="13" t="n"/>
+      <c r="C93" s="13" t="n"/>
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="12" t="n"/>
-      <c r="G93" s="12" t="n"/>
+      <c r="F93" s="13" t="n"/>
+      <c r="G93" s="13" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="n">
+      <c r="A94" s="11" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="10" t="n"/>
-      <c r="C94" s="10" t="n"/>
-      <c r="D94" s="11" t="n"/>
-      <c r="E94" s="11" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
+      <c r="B94" s="11" t="n"/>
+      <c r="C94" s="11" t="n"/>
+      <c r="D94" s="12" t="n"/>
+      <c r="E94" s="12" t="n"/>
+      <c r="F94" s="11" t="n"/>
+      <c r="G94" s="11" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="12" t="n">
+      <c r="A95" s="13" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="12" t="n"/>
-      <c r="C95" s="12" t="n"/>
+      <c r="B95" s="13" t="n"/>
+      <c r="C95" s="13" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="12" t="n"/>
-      <c r="G95" s="12" t="n"/>
+      <c r="F95" s="13" t="n"/>
+      <c r="G95" s="13" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="n">
+      <c r="A96" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="10" t="n"/>
-      <c r="C96" s="10" t="n"/>
-      <c r="D96" s="11" t="n"/>
-      <c r="E96" s="11" t="n"/>
-      <c r="F96" s="10" t="n"/>
-      <c r="G96" s="10" t="n"/>
+      <c r="B96" s="11" t="n"/>
+      <c r="C96" s="11" t="n"/>
+      <c r="D96" s="12" t="n"/>
+      <c r="E96" s="12" t="n"/>
+      <c r="F96" s="11" t="n"/>
+      <c r="G96" s="11" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="12" t="n">
+      <c r="A97" s="13" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="12" t="n"/>
-      <c r="C97" s="12" t="n"/>
+      <c r="B97" s="13" t="n"/>
+      <c r="C97" s="13" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
-      <c r="F97" s="12" t="n"/>
-      <c r="G97" s="12" t="n"/>
+      <c r="F97" s="13" t="n"/>
+      <c r="G97" s="13" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="n">
+      <c r="A98" s="11" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="10" t="n"/>
-      <c r="C98" s="10" t="n"/>
-      <c r="D98" s="11" t="n"/>
-      <c r="E98" s="11" t="n"/>
-      <c r="F98" s="10" t="n"/>
-      <c r="G98" s="10" t="n"/>
+      <c r="B98" s="11" t="n"/>
+      <c r="C98" s="11" t="n"/>
+      <c r="D98" s="12" t="n"/>
+      <c r="E98" s="12" t="n"/>
+      <c r="F98" s="11" t="n"/>
+      <c r="G98" s="11" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="12" t="n">
+      <c r="A99" s="13" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="12" t="n"/>
-      <c r="C99" s="12" t="n"/>
+      <c r="B99" s="13" t="n"/>
+      <c r="C99" s="13" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
-      <c r="F99" s="12" t="n"/>
-      <c r="G99" s="12" t="n"/>
+      <c r="F99" s="13" t="n"/>
+      <c r="G99" s="13" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="n">
+      <c r="A100" s="11" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="10" t="n"/>
-      <c r="C100" s="10" t="n"/>
-      <c r="D100" s="11" t="n"/>
-      <c r="E100" s="11" t="n"/>
-      <c r="F100" s="10" t="n"/>
-      <c r="G100" s="10" t="n"/>
+      <c r="B100" s="11" t="n"/>
+      <c r="C100" s="11" t="n"/>
+      <c r="D100" s="12" t="n"/>
+      <c r="E100" s="12" t="n"/>
+      <c r="F100" s="11" t="n"/>
+      <c r="G100" s="11" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="12" t="n">
+      <c r="A101" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="12" t="n"/>
-      <c r="C101" s="12" t="n"/>
+      <c r="B101" s="13" t="n"/>
+      <c r="C101" s="13" t="n"/>
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
-      <c r="F101" s="12" t="n"/>
-      <c r="G101" s="12" t="n"/>
+      <c r="F101" s="13" t="n"/>
+      <c r="G101" s="13" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="n">
+      <c r="A102" s="11" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="10" t="n"/>
-      <c r="C102" s="10" t="n"/>
-      <c r="D102" s="11" t="n"/>
-      <c r="E102" s="11" t="n"/>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="10" t="n"/>
+      <c r="B102" s="11" t="n"/>
+      <c r="C102" s="11" t="n"/>
+      <c r="D102" s="12" t="n"/>
+      <c r="E102" s="12" t="n"/>
+      <c r="F102" s="11" t="n"/>
+      <c r="G102" s="11" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="12" t="n">
+      <c r="A103" s="13" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="12" t="n"/>
-      <c r="C103" s="12" t="n"/>
+      <c r="B103" s="13" t="n"/>
+      <c r="C103" s="13" t="n"/>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="12" t="n"/>
-      <c r="G103" s="12" t="n"/>
+      <c r="F103" s="13" t="n"/>
+      <c r="G103" s="13" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="n">
+      <c r="A104" s="11" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="10" t="n"/>
-      <c r="C104" s="10" t="n"/>
-      <c r="D104" s="11" t="n"/>
-      <c r="E104" s="11" t="n"/>
-      <c r="F104" s="10" t="n"/>
-      <c r="G104" s="10" t="n"/>
+      <c r="B104" s="11" t="n"/>
+      <c r="C104" s="11" t="n"/>
+      <c r="D104" s="12" t="n"/>
+      <c r="E104" s="12" t="n"/>
+      <c r="F104" s="11" t="n"/>
+      <c r="G104" s="11" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="12" t="n">
+      <c r="A105" s="13" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="12" t="n"/>
-      <c r="C105" s="12" t="n"/>
+      <c r="B105" s="13" t="n"/>
+      <c r="C105" s="13" t="n"/>
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
-      <c r="F105" s="12" t="n"/>
-      <c r="G105" s="12" t="n"/>
+      <c r="F105" s="13" t="n"/>
+      <c r="G105" s="13" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="n">
+      <c r="A106" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="10" t="n"/>
-      <c r="C106" s="10" t="n"/>
-      <c r="D106" s="11" t="n"/>
-      <c r="E106" s="11" t="n"/>
-      <c r="F106" s="10" t="n"/>
-      <c r="G106" s="10" t="n"/>
+      <c r="B106" s="11" t="n"/>
+      <c r="C106" s="11" t="n"/>
+      <c r="D106" s="12" t="n"/>
+      <c r="E106" s="12" t="n"/>
+      <c r="F106" s="11" t="n"/>
+      <c r="G106" s="11" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="n">
+      <c r="A107" s="13" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="12" t="n"/>
-      <c r="C107" s="12" t="n"/>
+      <c r="B107" s="13" t="n"/>
+      <c r="C107" s="13" t="n"/>
       <c r="D107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
-      <c r="F107" s="12" t="n"/>
-      <c r="G107" s="12" t="n"/>
+      <c r="F107" s="13" t="n"/>
+      <c r="G107" s="13" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="n">
+      <c r="A108" s="11" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="10" t="n"/>
-      <c r="C108" s="10" t="n"/>
-      <c r="D108" s="11" t="n"/>
-      <c r="E108" s="11" t="n"/>
-      <c r="F108" s="10" t="n"/>
-      <c r="G108" s="10" t="n"/>
+      <c r="B108" s="11" t="n"/>
+      <c r="C108" s="11" t="n"/>
+      <c r="D108" s="12" t="n"/>
+      <c r="E108" s="12" t="n"/>
+      <c r="F108" s="11" t="n"/>
+      <c r="G108" s="11" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="12" t="n">
+      <c r="A109" s="13" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="12" t="n"/>
-      <c r="C109" s="12" t="n"/>
+      <c r="B109" s="13" t="n"/>
+      <c r="C109" s="13" t="n"/>
       <c r="D109" s="7" t="n"/>
       <c r="E109" s="7" t="n"/>
-      <c r="F109" s="12" t="n"/>
-      <c r="G109" s="12" t="n"/>
+      <c r="F109" s="13" t="n"/>
+      <c r="G109" s="13" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="n">
+      <c r="A110" s="11" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="10" t="n"/>
-      <c r="C110" s="10" t="n"/>
-      <c r="D110" s="11" t="n"/>
-      <c r="E110" s="11" t="n"/>
-      <c r="F110" s="10" t="n"/>
-      <c r="G110" s="10" t="n"/>
+      <c r="B110" s="11" t="n"/>
+      <c r="C110" s="11" t="n"/>
+      <c r="D110" s="12" t="n"/>
+      <c r="E110" s="12" t="n"/>
+      <c r="F110" s="11" t="n"/>
+      <c r="G110" s="11" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="12" t="n">
+      <c r="A111" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="12" t="n"/>
-      <c r="C111" s="12" t="n"/>
+      <c r="B111" s="13" t="n"/>
+      <c r="C111" s="13" t="n"/>
       <c r="D111" s="7" t="n"/>
       <c r="E111" s="7" t="n"/>
-      <c r="F111" s="12" t="n"/>
-      <c r="G111" s="12" t="n"/>
+      <c r="F111" s="13" t="n"/>
+      <c r="G111" s="13" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="10" t="n">
+      <c r="A112" s="11" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="10" t="n"/>
-      <c r="C112" s="10" t="n"/>
-      <c r="D112" s="11" t="n"/>
-      <c r="E112" s="11" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="10" t="n"/>
+      <c r="B112" s="11" t="n"/>
+      <c r="C112" s="11" t="n"/>
+      <c r="D112" s="12" t="n"/>
+      <c r="E112" s="12" t="n"/>
+      <c r="F112" s="11" t="n"/>
+      <c r="G112" s="11" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="12" t="n">
+      <c r="A113" s="13" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="12" t="n"/>
-      <c r="C113" s="12" t="n"/>
+      <c r="B113" s="13" t="n"/>
+      <c r="C113" s="13" t="n"/>
       <c r="D113" s="7" t="n"/>
       <c r="E113" s="7" t="n"/>
-      <c r="F113" s="12" t="n"/>
-      <c r="G113" s="12" t="n"/>
+      <c r="F113" s="13" t="n"/>
+      <c r="G113" s="13" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="10" t="n">
+      <c r="A114" s="11" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="10" t="n"/>
-      <c r="C114" s="10" t="n"/>
-      <c r="D114" s="11" t="n"/>
-      <c r="E114" s="11" t="n"/>
-      <c r="F114" s="10" t="n"/>
-      <c r="G114" s="10" t="n"/>
+      <c r="B114" s="11" t="n"/>
+      <c r="C114" s="11" t="n"/>
+      <c r="D114" s="12" t="n"/>
+      <c r="E114" s="12" t="n"/>
+      <c r="F114" s="11" t="n"/>
+      <c r="G114" s="11" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="12" t="n">
+      <c r="A115" s="13" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="12" t="n"/>
-      <c r="C115" s="12" t="n"/>
+      <c r="B115" s="13" t="n"/>
+      <c r="C115" s="13" t="n"/>
       <c r="D115" s="7" t="n"/>
       <c r="E115" s="7" t="n"/>
-      <c r="F115" s="12" t="n"/>
-      <c r="G115" s="12" t="n"/>
+      <c r="F115" s="13" t="n"/>
+      <c r="G115" s="13" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="10" t="n">
+      <c r="A116" s="11" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="10" t="n"/>
-      <c r="C116" s="10" t="n"/>
-      <c r="D116" s="11" t="n"/>
-      <c r="E116" s="11" t="n"/>
-      <c r="F116" s="10" t="n"/>
-      <c r="G116" s="10" t="n"/>
+      <c r="B116" s="11" t="n"/>
+      <c r="C116" s="11" t="n"/>
+      <c r="D116" s="12" t="n"/>
+      <c r="E116" s="12" t="n"/>
+      <c r="F116" s="11" t="n"/>
+      <c r="G116" s="11" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="12" t="n">
+      <c r="A117" s="13" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="12" t="n"/>
-      <c r="C117" s="12" t="n"/>
+      <c r="B117" s="13" t="n"/>
+      <c r="C117" s="13" t="n"/>
       <c r="D117" s="7" t="n"/>
       <c r="E117" s="7" t="n"/>
-      <c r="F117" s="12" t="n"/>
-      <c r="G117" s="12" t="n"/>
+      <c r="F117" s="13" t="n"/>
+      <c r="G117" s="13" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="10" t="n">
+      <c r="A118" s="11" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="10" t="n"/>
-      <c r="C118" s="10" t="n"/>
-      <c r="D118" s="11" t="n"/>
-      <c r="E118" s="11" t="n"/>
-      <c r="F118" s="10" t="n"/>
-      <c r="G118" s="10" t="n"/>
+      <c r="B118" s="11" t="n"/>
+      <c r="C118" s="11" t="n"/>
+      <c r="D118" s="12" t="n"/>
+      <c r="E118" s="12" t="n"/>
+      <c r="F118" s="11" t="n"/>
+      <c r="G118" s="11" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="12" t="n">
+      <c r="A119" s="13" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="12" t="n"/>
-      <c r="C119" s="12" t="n"/>
+      <c r="B119" s="13" t="n"/>
+      <c r="C119" s="13" t="n"/>
       <c r="D119" s="7" t="n"/>
       <c r="E119" s="7" t="n"/>
-      <c r="F119" s="12" t="n"/>
-      <c r="G119" s="12" t="n"/>
+      <c r="F119" s="13" t="n"/>
+      <c r="G119" s="13" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="10" t="n">
+      <c r="A120" s="11" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="10" t="n"/>
-      <c r="C120" s="10" t="n"/>
-      <c r="D120" s="11" t="n"/>
-      <c r="E120" s="11" t="n"/>
-      <c r="F120" s="10" t="n"/>
-      <c r="G120" s="10" t="n"/>
+      <c r="B120" s="11" t="n"/>
+      <c r="C120" s="11" t="n"/>
+      <c r="D120" s="12" t="n"/>
+      <c r="E120" s="12" t="n"/>
+      <c r="F120" s="11" t="n"/>
+      <c r="G120" s="11" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -2530,12 +2538,12 @@
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>3번 항목</t>
         </is>
@@ -2548,15 +2556,15 @@
 → ②라면 블로그와 링크드인 주소를 알려주세요.</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr"/>
+      <c r="D2" s="16" t="inlineStr"/>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>5번 항목</t>
         </is>
@@ -2567,15 +2575,15 @@
 보내주신 문서에 물음표가 붙어 있어 확인드립니다. 다른 후보가 있으면 함께 알려주세요.</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr"/>
+      <c r="D3" s="16" t="inlineStr"/>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>8번 항목</t>
         </is>
@@ -2586,15 +2594,15 @@
 예: 누적 출원 건수, 자문 기업 수, 상담 회신 시간 등.</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr"/>
+      <c r="D4" s="16" t="inlineStr"/>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>15번 항목</t>
         </is>
@@ -2605,15 +2613,15 @@
 ① 의료소송 수행 목록  ② 자문 목록  ③ 출원 목록(수술도구·슬리퍼 등)</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr"/>
+      <c r="D5" s="16" t="inlineStr"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>16번 항목</t>
         </is>
@@ -2624,15 +2632,15 @@
 책 제목과 함께, 책별로 무료배포 링크 또는 구매 페이지 주소를 알려주세요.</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr"/>
+      <c r="D6" s="16" t="inlineStr"/>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>18번 항목</t>
         </is>
@@ -2644,15 +2652,15 @@
 부가세 별도 여부도 알려주세요.</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr"/>
+      <c r="D7" s="16" t="inlineStr"/>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Q7</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>20번 항목</t>
         </is>
@@ -2663,7 +2671,7 @@
 (예: 소개 페이지의 참고 자료로 소개 / 반영하지 않음)</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr"/>
+      <c r="D8" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3021,189 +3029,189 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>02-1234-5678 (임시)</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr"/>
+      <c r="C2" s="19" t="inlineStr"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>이메일</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>contact@example.com (임시)</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr"/>
+      <c r="C3" s="19" t="inlineStr"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>서울특별시 서초구 반포대로 00, 0층 (임시)</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr"/>
+      <c r="C4" s="19" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>상담 가능 시간</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>평일 09:00–18:00, 점심 12:00–13:00 (임시)</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr"/>
+      <c r="C5" s="19" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>카카오톡 채널 주소</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>임시 링크</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr"/>
+      <c r="C6" s="19" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>실적 수치 ① 누적 출원·등록</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>3,200+ (예시)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr"/>
+      <c r="C7" s="19" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>실적 수치 ② 상표 등록 성공률</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>98% (예시)</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr"/>
+      <c r="C8" s="19" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>실적 수치 ③ 실무 경력</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>15년+ (예시)</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>실적 수치 ④ 상담 회신</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>24시간 이내 (예시)</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr"/>
+      <c r="C10" s="19" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>로고 파일</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>없음 — 글자 '오'로 임시 표시</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>대표 프로필 사진</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>없음 — 회색 박스로 임시 표시</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr"/>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>수령 완료 — 소개 페이지에 반영됨 (확인 요청)</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>지도 사용 여부</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>빈 박스</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr"/>
+      <c r="C13" s="19" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>상담 신청 접수 방법</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr"/>
+      <c r="C14" s="19" t="inlineStr"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>사이트 주소(도메인)</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr"/>
+      <c r="C15" s="19" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>※ 로고 파일과 대표 사진은 파일을 메일·카톡으로 함께 보내 주세요. (PNG/JPG, 가능한 원본 크기)</t>
         </is>
